--- a/reports/pdf_change_20260717.xlsx
+++ b/reports/pdf_change_20260717.xlsx
@@ -577,7 +577,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      당일 2026-07-17  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 545억   ·   현금 9억(1.6%)      당일 2026-07-17  vs  전영업일 2026-07-16      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
